--- a/results/lcc_analysis.xlsx
+++ b/results/lcc_analysis.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,41 +431,61 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LCC ASHP (BHD)</t>
+          <t>Annual ASHP electricity (kWh)</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15524</v>
+        <v>11534.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LCC SA-GSHP (BHD)</t>
+          <t>Annual SA-GSHP electricity (kWh)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15921</v>
+        <v>8679</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NPV @ 0.030 BHD/kWh</t>
+          <t>LCC ASHP @ 0.030 BHD/kWh</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-397</v>
+        <v>8628.74</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NPV @ 0.040 BHD/kWh</t>
+          <t>LCC SA-GSHP @ 0.030 BHD/kWh</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3142</v>
+        <v>13268.98</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NPV @ 0.030 BHD/kWh</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>-4640.24</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Simple payback (years)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>62.7</v>
       </c>
     </row>
   </sheetData>
